--- a/VerveStacks_USA_grids_syn_10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_USA_grids_syn_10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA_grids_syn_10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{438D4CA2-A75F-4EC6-9A5F-7C6F5266B378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB310E41-156E-4B18-BEB5-90DF137D8079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -12910,28 +12910,28 @@
         <v>77</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
@@ -12990,11 +12990,11 @@
       </c>
       <c r="F20">
         <f>C11</f>
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <f>D11</f>
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -13020,11 +13020,11 @@
       </c>
       <c r="F21">
         <f>E11</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <f>F11</f>
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -13050,11 +13050,11 @@
       </c>
       <c r="F22">
         <f>G11</f>
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <f>H11</f>
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -13080,11 +13080,11 @@
       </c>
       <c r="F23">
         <f>I11</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <f>J11</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>4</v>
